--- a/opioid_trends/files for tableau/top15_horserace_graph.xlsx
+++ b/opioid_trends/files for tableau/top15_horserace_graph.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t xml:space="preserve">geography</t>
   </si>
@@ -83,6 +83,9 @@
     <t xml:space="preserve">Pennsylvania</t>
   </si>
   <si>
+    <t xml:space="preserve">Arizona</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vermont</t>
   </si>
   <si>
@@ -92,9 +95,6 @@
     <t xml:space="preserve">North Carolina</t>
   </si>
   <si>
-    <t xml:space="preserve">Arizona</t>
-  </si>
-  <si>
     <t xml:space="preserve">Florida</t>
   </si>
   <si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t xml:space="preserve">Massachusetts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Colorado</t>
   </si>
   <si>
     <t xml:space="preserve">New Jersey</t>
@@ -807,87 +810,87 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B22" s="1" t="n">
-        <v>44896</v>
+        <v>45992</v>
       </c>
       <c r="C22" t="n">
-        <v>2309</v>
+        <v>351</v>
       </c>
       <c r="D22" t="n">
-        <v>51.3780052739778</v>
+        <v>51.3793376017706</v>
       </c>
       <c r="E22" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="C23" t="n">
-        <v>502</v>
+        <v>2309</v>
       </c>
       <c r="D23" t="n">
-        <v>51.1257857279619</v>
+        <v>51.3780052739778</v>
       </c>
       <c r="E23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B24" s="1" t="n">
-        <v>43070</v>
+        <v>44531</v>
       </c>
       <c r="C24" t="n">
-        <v>348</v>
+        <v>502</v>
       </c>
       <c r="D24" t="n">
-        <v>50.9401979641486</v>
+        <v>51.1257857279619</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B25" s="1" t="n">
-        <v>44531</v>
+        <v>43070</v>
       </c>
       <c r="C25" t="n">
-        <v>1040</v>
+        <v>348</v>
       </c>
       <c r="D25" t="n">
-        <v>49.3039140670704</v>
+        <v>50.9401979641486</v>
       </c>
       <c r="E25" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B26" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="C26" t="n">
-        <v>882</v>
+        <v>1040</v>
       </c>
       <c r="D26" t="n">
-        <v>48.971460521063</v>
+        <v>49.3039140670704</v>
       </c>
       <c r="E26" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27">
@@ -895,13 +898,13 @@
         <v>6</v>
       </c>
       <c r="B27" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="C27" t="n">
-        <v>879</v>
+        <v>882</v>
       </c>
       <c r="D27" t="n">
-        <v>48.8048909274539</v>
+        <v>48.971460521063</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
@@ -909,390 +912,390 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="B28" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="C28" t="n">
-        <v>357</v>
+        <v>879</v>
       </c>
       <c r="D28" t="n">
-        <v>48.5086642996613</v>
+        <v>48.8048909274539</v>
       </c>
       <c r="E28" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B29" s="1" t="n">
         <v>45261</v>
       </c>
       <c r="C29" t="n">
-        <v>2255</v>
+        <v>357</v>
       </c>
       <c r="D29" t="n">
-        <v>48.4185596605762</v>
+        <v>48.5086642996613</v>
       </c>
       <c r="E29" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="B30" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="C30" t="n">
-        <v>1473</v>
+        <v>2255</v>
       </c>
       <c r="D30" t="n">
-        <v>48.1492450080706</v>
+        <v>48.4185596605762</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B31" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="C31" t="n">
-        <v>1007</v>
+        <v>1473</v>
       </c>
       <c r="D31" t="n">
-        <v>47.7394629476345</v>
+        <v>48.1492450080706</v>
       </c>
       <c r="E31" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B32" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="C32" t="n">
-        <v>2131</v>
+        <v>1007</v>
       </c>
       <c r="D32" t="n">
-        <v>47.4172928708734</v>
+        <v>47.7394629476345</v>
       </c>
       <c r="E32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B33" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="C33" t="n">
-        <v>852</v>
+        <v>2131</v>
       </c>
       <c r="D33" t="n">
-        <v>47.3057645849724</v>
+        <v>47.4172928708734</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="B34" s="1" t="n">
-        <v>45261</v>
+        <v>43800</v>
       </c>
       <c r="C34" t="n">
-        <v>994</v>
+        <v>852</v>
       </c>
       <c r="D34" t="n">
-        <v>47.1231640217961</v>
+        <v>47.3057645849724</v>
       </c>
       <c r="E34" t="n">
-        <v>8</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="B35" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="C35" t="n">
-        <v>2104</v>
+        <v>994</v>
       </c>
       <c r="D35" t="n">
-        <v>46.816510652425</v>
+        <v>47.1231640217961</v>
       </c>
       <c r="E35" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="B36" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="C36" t="n">
-        <v>3512</v>
+        <v>2104</v>
       </c>
       <c r="D36" t="n">
-        <v>46.1051880939391</v>
+        <v>46.816510652425</v>
       </c>
       <c r="E36" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B37" s="1" t="n">
-        <v>45627</v>
+        <v>45261</v>
       </c>
       <c r="C37" t="n">
-        <v>339</v>
+        <v>3512</v>
       </c>
       <c r="D37" t="n">
-        <v>46.0628492929556</v>
+        <v>46.1051880939391</v>
       </c>
       <c r="E37" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B38" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="C38" t="n">
-        <v>5405</v>
+        <v>339</v>
       </c>
       <c r="D38" t="n">
-        <v>45.9221355993578</v>
+        <v>46.0628492929556</v>
       </c>
       <c r="E38" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B39" s="1" t="n">
-        <v>45261</v>
+        <v>44531</v>
       </c>
       <c r="C39" t="n">
-        <v>1400</v>
+        <v>5405</v>
       </c>
       <c r="D39" t="n">
-        <v>45.7630298786822</v>
+        <v>45.9221355993578</v>
       </c>
       <c r="E39" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B40" s="1" t="n">
-        <v>44166</v>
+        <v>45261</v>
       </c>
       <c r="C40" t="n">
-        <v>449</v>
+        <v>1400</v>
       </c>
       <c r="D40" t="n">
-        <v>45.7280434100695</v>
+        <v>45.7630298786822</v>
       </c>
       <c r="E40" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B41" s="1" t="n">
-        <v>44531</v>
+        <v>44166</v>
       </c>
       <c r="C41" t="n">
-        <v>620</v>
+        <v>449</v>
       </c>
       <c r="D41" t="n">
-        <v>45.687471168995</v>
+        <v>45.7280434100695</v>
       </c>
       <c r="E41" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B42" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="C42" t="n">
-        <v>819</v>
+        <v>620</v>
       </c>
       <c r="D42" t="n">
-        <v>45.4734990552728</v>
+        <v>45.687471168995</v>
       </c>
       <c r="E42" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="B43" s="1" t="n">
-        <v>44896</v>
+        <v>45627</v>
       </c>
       <c r="C43" t="n">
-        <v>2292</v>
+        <v>819</v>
       </c>
       <c r="D43" t="n">
-        <v>45.1278553656173</v>
+        <v>45.4734990552728</v>
       </c>
       <c r="E43" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B44" s="1" t="n">
-        <v>44166</v>
+        <v>44896</v>
       </c>
       <c r="C44" t="n">
-        <v>3090</v>
+        <v>2292</v>
       </c>
       <c r="D44" t="n">
-        <v>45.0470347898687</v>
+        <v>45.1278553656173</v>
       </c>
       <c r="E44" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="B45" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="C45" t="n">
-        <v>2761</v>
+        <v>951</v>
       </c>
       <c r="D45" t="n">
-        <v>44.9049327930429</v>
+        <v>45.0846368055615</v>
       </c>
       <c r="E45" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="B46" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="C46" t="n">
-        <v>5215</v>
+        <v>3090</v>
       </c>
       <c r="D46" t="n">
-        <v>44.30785146173</v>
+        <v>45.0470347898687</v>
       </c>
       <c r="E46" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="B47" s="1" t="n">
-        <v>44531</v>
+        <v>45992</v>
       </c>
       <c r="C47" t="n">
-        <v>2724</v>
+        <v>331</v>
       </c>
       <c r="D47" t="n">
-        <v>44.303164407189</v>
+        <v>44.9758204010865</v>
       </c>
       <c r="E47" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B48" s="1" t="n">
-        <v>45261</v>
+        <v>44166</v>
       </c>
       <c r="C48" t="n">
-        <v>1851</v>
+        <v>2761</v>
       </c>
       <c r="D48" t="n">
-        <v>43.9962473649195</v>
+        <v>44.9049327930429</v>
       </c>
       <c r="E48" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B49" s="1" t="n">
-        <v>42705</v>
+        <v>44166</v>
       </c>
       <c r="C49" t="n">
-        <v>300</v>
+        <v>5215</v>
       </c>
       <c r="D49" t="n">
-        <v>43.9139637621971</v>
+        <v>44.30785146173</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B50" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="C50" t="n">
-        <v>5144</v>
+        <v>2724</v>
       </c>
       <c r="D50" t="n">
-        <v>43.7046189681955</v>
+        <v>44.303164407189</v>
       </c>
       <c r="E50" t="n">
         <v>10</v>
@@ -1300,373 +1303,373 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="B51" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="C51" t="n">
-        <v>5138</v>
+        <v>1851</v>
       </c>
       <c r="D51" t="n">
-        <v>43.6536415743756</v>
+        <v>43.9962473649195</v>
       </c>
       <c r="E51" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B52" s="1" t="n">
-        <v>45261</v>
+        <v>42705</v>
       </c>
       <c r="C52" t="n">
-        <v>592</v>
+        <v>300</v>
       </c>
       <c r="D52" t="n">
-        <v>43.6241660194275</v>
+        <v>43.9139637621971</v>
       </c>
       <c r="E52" t="n">
-        <v>12</v>
+        <v>2</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="B53" s="1" t="n">
-        <v>44531</v>
+        <v>44896</v>
       </c>
       <c r="C53" t="n">
-        <v>1562</v>
+        <v>5144</v>
       </c>
       <c r="D53" t="n">
-        <v>43.3247441981733</v>
+        <v>43.7046189681955</v>
       </c>
       <c r="E53" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="B54" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="C54" t="n">
-        <v>295</v>
+        <v>5138</v>
       </c>
       <c r="D54" t="n">
-        <v>43.1820643661605</v>
+        <v>43.6536415743756</v>
       </c>
       <c r="E54" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B55" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="C55" t="n">
-        <v>423</v>
+        <v>592</v>
       </c>
       <c r="D55" t="n">
-        <v>43.0800943484619</v>
+        <v>43.6241660194275</v>
       </c>
       <c r="E55" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B56" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="C56" t="n">
-        <v>2166</v>
+        <v>1562</v>
       </c>
       <c r="D56" t="n">
-        <v>42.6470046779787</v>
+        <v>43.3247441981733</v>
       </c>
       <c r="E56" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="B57" s="1" t="n">
-        <v>45261</v>
+        <v>43435</v>
       </c>
       <c r="C57" t="n">
-        <v>2153</v>
+        <v>295</v>
       </c>
       <c r="D57" t="n">
-        <v>42.3910438927461</v>
+        <v>43.1820643661605</v>
       </c>
       <c r="E57" t="n">
-        <v>13</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="B58" s="1" t="n">
-        <v>44531</v>
+        <v>43800</v>
       </c>
       <c r="C58" t="n">
-        <v>460</v>
+        <v>423</v>
       </c>
       <c r="D58" t="n">
-        <v>42.1265095714177</v>
+        <v>43.0800943484619</v>
       </c>
       <c r="E58" t="n">
-        <v>13</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B59" s="1" t="n">
         <v>44531</v>
       </c>
       <c r="C59" t="n">
-        <v>5444</v>
+        <v>2166</v>
       </c>
       <c r="D59" t="n">
-        <v>41.9716822210144</v>
+        <v>42.6470046779787</v>
       </c>
       <c r="E59" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="B60" s="1" t="n">
-        <v>43070</v>
+        <v>45261</v>
       </c>
       <c r="C60" t="n">
-        <v>5434</v>
+        <v>2153</v>
       </c>
       <c r="D60" t="n">
-        <v>41.8945850824747</v>
+        <v>42.3910438927461</v>
       </c>
       <c r="E60" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="B61" s="1" t="n">
-        <v>45627</v>
+        <v>44531</v>
       </c>
       <c r="C61" t="n">
-        <v>3183</v>
+        <v>460</v>
       </c>
       <c r="D61" t="n">
-        <v>41.7861086853667</v>
+        <v>42.1265095714177</v>
       </c>
       <c r="E61" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B62" s="1" t="n">
-        <v>44896</v>
+        <v>44531</v>
       </c>
       <c r="C62" t="n">
-        <v>266</v>
+        <v>5444</v>
       </c>
       <c r="D62" t="n">
-        <v>41.456462142925</v>
+        <v>41.9716822210144</v>
       </c>
       <c r="E62" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="B63" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="C63" t="n">
-        <v>1929</v>
+        <v>2969</v>
       </c>
       <c r="D63" t="n">
-        <v>41.4188033637479</v>
+        <v>41.9397494322454</v>
       </c>
       <c r="E63" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B64" s="1" t="n">
-        <v>44896</v>
+        <v>43070</v>
       </c>
       <c r="C64" t="n">
-        <v>452</v>
+        <v>5434</v>
       </c>
       <c r="D64" t="n">
-        <v>41.3938746223496</v>
+        <v>41.8945850824747</v>
       </c>
       <c r="E64" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="B65" s="1" t="n">
-        <v>44531</v>
+        <v>45627</v>
       </c>
       <c r="C65" t="n">
-        <v>2789</v>
+        <v>3183</v>
       </c>
       <c r="D65" t="n">
-        <v>41.310317655458</v>
+        <v>41.7861086853667</v>
       </c>
       <c r="E65" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B66" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="C66" t="n">
-        <v>4255</v>
+        <v>266</v>
       </c>
       <c r="D66" t="n">
-        <v>41.0436092447764</v>
+        <v>41.456462142925</v>
       </c>
       <c r="E66" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B67" s="1" t="n">
-        <v>44896</v>
+        <v>44166</v>
       </c>
       <c r="C67" t="n">
-        <v>2523</v>
+        <v>1929</v>
       </c>
       <c r="D67" t="n">
-        <v>41.0340983110638</v>
+        <v>41.4188033637479</v>
       </c>
       <c r="E67" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B68" s="1" t="n">
         <v>44896</v>
       </c>
       <c r="C68" t="n">
-        <v>1476</v>
+        <v>452</v>
       </c>
       <c r="D68" t="n">
-        <v>40.9393869631906</v>
+        <v>41.3938746223496</v>
       </c>
       <c r="E68" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="B69" s="1" t="n">
-        <v>43435</v>
+        <v>44531</v>
       </c>
       <c r="C69" t="n">
-        <v>399</v>
+        <v>2789</v>
       </c>
       <c r="D69" t="n">
-        <v>40.6358336762088</v>
+        <v>41.310317655458</v>
       </c>
       <c r="E69" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>18</v>
+        <v>26</v>
       </c>
       <c r="B70" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="C70" t="n">
-        <v>2493</v>
+        <v>4255</v>
       </c>
       <c r="D70" t="n">
-        <v>40.5461779982093</v>
+        <v>41.0436092447764</v>
       </c>
       <c r="E70" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="B71" s="1" t="n">
-        <v>42339</v>
+        <v>44896</v>
       </c>
       <c r="C71" t="n">
-        <v>729</v>
+        <v>2523</v>
       </c>
       <c r="D71" t="n">
-        <v>40.4764112470011</v>
+        <v>41.0340983110638</v>
       </c>
       <c r="E71" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B72" s="1" t="n">
-        <v>45261</v>
+        <v>44896</v>
       </c>
       <c r="C72" t="n">
-        <v>4745</v>
+        <v>1476</v>
       </c>
       <c r="D72" t="n">
-        <v>40.3146222791772</v>
+        <v>40.9393869631906</v>
       </c>
       <c r="E72" t="n">
         <v>15</v>
@@ -1674,19 +1677,19 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B73" s="1" t="n">
-        <v>44166</v>
+        <v>43435</v>
       </c>
       <c r="C73" t="n">
-        <v>5178</v>
+        <v>399</v>
       </c>
       <c r="D73" t="n">
-        <v>39.9208983358583</v>
+        <v>40.6358336762088</v>
       </c>
       <c r="E73" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -1694,404 +1697,404 @@
         <v>18</v>
       </c>
       <c r="B74" s="1" t="n">
-        <v>43435</v>
+        <v>45261</v>
       </c>
       <c r="C74" t="n">
-        <v>2393</v>
+        <v>2493</v>
       </c>
       <c r="D74" t="n">
-        <v>38.919776955361</v>
+        <v>40.5461779982093</v>
       </c>
       <c r="E74" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B75" s="1" t="n">
-        <v>44166</v>
+        <v>42339</v>
       </c>
       <c r="C75" t="n">
-        <v>1385</v>
+        <v>729</v>
       </c>
       <c r="D75" t="n">
-        <v>38.4153461680345</v>
+        <v>40.4764112470011</v>
       </c>
       <c r="E75" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B76" s="1" t="n">
-        <v>43800</v>
+        <v>45261</v>
       </c>
       <c r="C76" t="n">
-        <v>2360</v>
+        <v>4745</v>
       </c>
       <c r="D76" t="n">
-        <v>38.383064611221</v>
+        <v>40.3146222791772</v>
       </c>
       <c r="E76" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B77" s="1" t="n">
-        <v>44166</v>
+        <v>45992</v>
       </c>
       <c r="C77" t="n">
-        <v>792</v>
+        <v>1225</v>
       </c>
       <c r="D77" t="n">
-        <v>37.5468268664613</v>
+        <v>40.0426511438469</v>
       </c>
       <c r="E77" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="B78" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="C78" t="n">
-        <v>2644</v>
+        <v>5178</v>
       </c>
       <c r="D78" t="n">
-        <v>37.3488371501707</v>
+        <v>39.9208983358583</v>
       </c>
       <c r="E78" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="B79" s="1" t="n">
-        <v>45627</v>
+        <v>43435</v>
       </c>
       <c r="C79" t="n">
-        <v>2555</v>
+        <v>2393</v>
       </c>
       <c r="D79" t="n">
-        <v>37.2476290900047</v>
+        <v>38.919776955361</v>
       </c>
       <c r="E79" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B80" s="1" t="n">
-        <v>45627</v>
+        <v>45992</v>
       </c>
       <c r="C80" t="n">
-        <v>784</v>
+        <v>2953</v>
       </c>
       <c r="D80" t="n">
-        <v>37.1675659890223</v>
+        <v>38.7666914696475</v>
       </c>
       <c r="E80" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="B81" s="1" t="n">
-        <v>43070</v>
+        <v>44166</v>
       </c>
       <c r="C81" t="n">
-        <v>2284</v>
+        <v>1385</v>
       </c>
       <c r="D81" t="n">
-        <v>37.1469998186563</v>
+        <v>38.4153461680345</v>
       </c>
       <c r="E81" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B82" s="1" t="n">
-        <v>42705</v>
+        <v>43800</v>
       </c>
       <c r="C82" t="n">
-        <v>4326</v>
+        <v>2360</v>
       </c>
       <c r="D82" t="n">
-        <v>36.7547009440928</v>
+        <v>38.383064611221</v>
       </c>
       <c r="E82" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="B83" s="1" t="n">
         <v>44166</v>
       </c>
       <c r="C83" t="n">
-        <v>397</v>
+        <v>792</v>
       </c>
       <c r="D83" t="n">
-        <v>36.3570093475062</v>
+        <v>37.5468268664613</v>
       </c>
       <c r="E83" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="B84" s="1" t="n">
-        <v>43800</v>
+        <v>44166</v>
       </c>
       <c r="C84" t="n">
-        <v>4279</v>
+        <v>2644</v>
       </c>
       <c r="D84" t="n">
-        <v>36.3553780258376</v>
+        <v>37.3488371501707</v>
       </c>
       <c r="E84" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="B85" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="C85" t="n">
-        <v>1529</v>
+        <v>2555</v>
       </c>
       <c r="D85" t="n">
-        <v>36.3426592225618</v>
+        <v>37.2476290900047</v>
       </c>
       <c r="E85" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B86" s="1" t="n">
-        <v>44166</v>
+        <v>45627</v>
       </c>
       <c r="C86" t="n">
-        <v>490</v>
+        <v>784</v>
       </c>
       <c r="D86" t="n">
-        <v>36.1078401174315</v>
+        <v>37.1675659890223</v>
       </c>
       <c r="E86" t="n">
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="B87" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="C87" t="n">
-        <v>4648</v>
+        <v>2284</v>
       </c>
       <c r="D87" t="n">
-        <v>35.834749993254</v>
+        <v>37.1469998186563</v>
       </c>
       <c r="E87" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>26</v>
+        <v>16</v>
       </c>
       <c r="B88" s="1" t="n">
-        <v>45627</v>
+        <v>42705</v>
       </c>
       <c r="C88" t="n">
-        <v>2531</v>
+        <v>4326</v>
       </c>
       <c r="D88" t="n">
-        <v>35.7526122644032</v>
+        <v>36.7547009440928</v>
       </c>
       <c r="E88" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B89" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="C89" t="n">
-        <v>351</v>
+        <v>397</v>
       </c>
       <c r="D89" t="n">
-        <v>35.7473123317025</v>
+        <v>36.3570093475062</v>
       </c>
       <c r="E89" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B90" s="1" t="n">
-        <v>44166</v>
+        <v>43800</v>
       </c>
       <c r="C90" t="n">
-        <v>7568</v>
+        <v>4279</v>
       </c>
       <c r="D90" t="n">
-        <v>35.4643130509141</v>
+        <v>36.3553780258376</v>
       </c>
       <c r="E90" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B91" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="C91" t="n">
-        <v>478</v>
+        <v>1529</v>
       </c>
       <c r="D91" t="n">
-        <v>35.2235664819026</v>
+        <v>36.3426592225618</v>
       </c>
       <c r="E91" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B92" s="1" t="n">
-        <v>43070</v>
+        <v>44166</v>
       </c>
       <c r="C92" t="n">
-        <v>1566</v>
+        <v>490</v>
       </c>
       <c r="D92" t="n">
-        <v>34.8453686700083</v>
+        <v>36.1078401174315</v>
       </c>
       <c r="E92" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B93" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="C93" t="n">
-        <v>478</v>
+        <v>4648</v>
       </c>
       <c r="D93" t="n">
-        <v>34.835206879589</v>
+        <v>35.834749993254</v>
       </c>
       <c r="E93" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="B94" s="1" t="n">
-        <v>43070</v>
+        <v>45627</v>
       </c>
       <c r="C94" t="n">
-        <v>341</v>
+        <v>2531</v>
       </c>
       <c r="D94" t="n">
-        <v>34.7288703849303</v>
+        <v>35.7526122644032</v>
       </c>
       <c r="E94" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="B95" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="C95" t="n">
-        <v>4444</v>
+        <v>351</v>
       </c>
       <c r="D95" t="n">
-        <v>34.2619683670441</v>
+        <v>35.7473123317025</v>
       </c>
       <c r="E95" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>10</v>
+        <v>27</v>
       </c>
       <c r="B96" s="1" t="n">
-        <v>45627</v>
+        <v>44166</v>
       </c>
       <c r="C96" t="n">
-        <v>1538</v>
+        <v>7568</v>
       </c>
       <c r="D96" t="n">
-        <v>34.2223352582841</v>
+        <v>35.4643130509141</v>
       </c>
       <c r="E96" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="B97" s="1" t="n">
-        <v>43800</v>
+        <v>45992</v>
       </c>
       <c r="C97" t="n">
-        <v>1231</v>
+        <v>637</v>
       </c>
       <c r="D97" t="n">
-        <v>34.1438925146935</v>
+        <v>35.3682770429899</v>
       </c>
       <c r="E97" t="n">
         <v>7</v>
@@ -2099,33 +2102,33 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B98" s="1" t="n">
-        <v>43435</v>
+        <v>45627</v>
       </c>
       <c r="C98" t="n">
-        <v>4415</v>
+        <v>478</v>
       </c>
       <c r="D98" t="n">
-        <v>34.0383866652789</v>
+        <v>35.2235664819026</v>
       </c>
       <c r="E98" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="B99" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="C99" t="n">
-        <v>4004</v>
+        <v>1566</v>
       </c>
       <c r="D99" t="n">
-        <v>34.018914142429</v>
+        <v>34.8453686700083</v>
       </c>
       <c r="E99" t="n">
         <v>6</v>
@@ -2133,206 +2136,206 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>18</v>
+        <v>28</v>
       </c>
       <c r="B100" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="C100" t="n">
-        <v>2074</v>
+        <v>478</v>
       </c>
       <c r="D100" t="n">
-        <v>33.7315576286748</v>
+        <v>34.835206879589</v>
       </c>
       <c r="E100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>28</v>
+        <v>8</v>
       </c>
       <c r="B101" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="C101" t="n">
-        <v>458</v>
+        <v>341</v>
       </c>
       <c r="D101" t="n">
-        <v>33.3776668427861</v>
+        <v>34.7288703849303</v>
       </c>
       <c r="E101" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="B102" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="C102" t="n">
-        <v>446</v>
+        <v>4444</v>
       </c>
       <c r="D102" t="n">
-        <v>32.5031428207044</v>
+        <v>34.2619683670441</v>
       </c>
       <c r="E102" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B103" s="1" t="n">
         <v>45627</v>
       </c>
       <c r="C103" t="n">
-        <v>1503</v>
+        <v>1538</v>
       </c>
       <c r="D103" t="n">
-        <v>32.2718825586901</v>
+        <v>34.2223352582841</v>
       </c>
       <c r="E103" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="B104" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="C104" t="n">
-        <v>2238</v>
+        <v>1231</v>
       </c>
       <c r="D104" t="n">
-        <v>32.0086866827273</v>
+        <v>34.1438925146935</v>
       </c>
       <c r="E104" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="B105" s="1" t="n">
-        <v>42705</v>
+        <v>43435</v>
       </c>
       <c r="C105" t="n">
-        <v>1437</v>
+        <v>4415</v>
       </c>
       <c r="D105" t="n">
-        <v>31.9749647374215</v>
+        <v>34.0383866652789</v>
       </c>
       <c r="E105" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="B106" s="1" t="n">
-        <v>45627</v>
+        <v>43435</v>
       </c>
       <c r="C106" t="n">
-        <v>205</v>
+        <v>4004</v>
       </c>
       <c r="D106" t="n">
-        <v>31.9495290951114</v>
+        <v>34.018914142429</v>
       </c>
       <c r="E106" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="B107" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="C107" t="n">
-        <v>346</v>
+        <v>2074</v>
       </c>
       <c r="D107" t="n">
-        <v>31.6864615471968</v>
+        <v>33.7315576286748</v>
       </c>
       <c r="E107" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B108" s="1" t="n">
-        <v>43800</v>
+        <v>42705</v>
       </c>
       <c r="C108" t="n">
-        <v>2215</v>
+        <v>458</v>
       </c>
       <c r="D108" t="n">
-        <v>31.6797323513141</v>
+        <v>33.3776668427861</v>
       </c>
       <c r="E108" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>29</v>
+        <v>8</v>
       </c>
       <c r="B109" s="1" t="n">
-        <v>42705</v>
+        <v>45992</v>
       </c>
       <c r="C109" t="n">
-        <v>2198</v>
+        <v>327</v>
       </c>
       <c r="D109" t="n">
-        <v>31.436592193313</v>
+        <v>33.3030516594493</v>
       </c>
       <c r="E109" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s">
+        <v>28</v>
+      </c>
+      <c r="B110" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="C110" t="n">
+        <v>446</v>
+      </c>
+      <c r="D110" t="n">
+        <v>32.5031428207044</v>
+      </c>
+      <c r="E110" t="n">
         <v>7</v>
-      </c>
-      <c r="B110" s="1" t="n">
-        <v>43800</v>
-      </c>
-      <c r="C110" t="n">
-        <v>2138</v>
-      </c>
-      <c r="D110" t="n">
-        <v>31.1684661426341</v>
-      </c>
-      <c r="E110" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="B111" s="1" t="n">
-        <v>43435</v>
+        <v>45627</v>
       </c>
       <c r="C111" t="n">
-        <v>2857</v>
+        <v>1503</v>
       </c>
       <c r="D111" t="n">
-        <v>30.9399239161605</v>
+        <v>32.2718825586901</v>
       </c>
       <c r="E111" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="112">
@@ -2340,50 +2343,50 @@
         <v>29</v>
       </c>
       <c r="B112" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="C112" t="n">
-        <v>2138</v>
+        <v>2238</v>
       </c>
       <c r="D112" t="n">
-        <v>30.5784504591916</v>
+        <v>32.0086866827273</v>
       </c>
       <c r="E112" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B113" s="1" t="n">
-        <v>45627</v>
+        <v>42705</v>
       </c>
       <c r="C113" t="n">
-        <v>333</v>
+        <v>1437</v>
       </c>
       <c r="D113" t="n">
-        <v>30.4959297549611</v>
+        <v>31.9749647374215</v>
       </c>
       <c r="E113" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="B114" s="1" t="n">
-        <v>43800</v>
+        <v>45627</v>
       </c>
       <c r="C114" t="n">
-        <v>1369</v>
+        <v>205</v>
       </c>
       <c r="D114" t="n">
-        <v>30.4618835946625</v>
+        <v>31.9495290951114</v>
       </c>
       <c r="E114" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
     </row>
     <row r="115">
@@ -2391,135 +2394,135 @@
         <v>21</v>
       </c>
       <c r="B115" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="C115" t="n">
-        <v>332</v>
+        <v>346</v>
       </c>
       <c r="D115" t="n">
-        <v>30.4043503863276</v>
+        <v>31.6864615471968</v>
       </c>
       <c r="E115" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="B116" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="C116" t="n">
-        <v>331</v>
+        <v>2215</v>
       </c>
       <c r="D116" t="n">
-        <v>30.3127710176941</v>
+        <v>31.6797323513141</v>
       </c>
       <c r="E116" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B117" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="C117" t="n">
-        <v>415</v>
+        <v>1813</v>
       </c>
       <c r="D117" t="n">
-        <v>30.2439557636599</v>
+        <v>31.6782150330516</v>
       </c>
       <c r="E117" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B118" s="1" t="n">
-        <v>43070</v>
+        <v>42705</v>
       </c>
       <c r="C118" t="n">
-        <v>409</v>
+        <v>2198</v>
       </c>
       <c r="D118" t="n">
-        <v>30.1389930776112</v>
+        <v>31.436592193313</v>
       </c>
       <c r="E118" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="B119" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="C119" t="n">
-        <v>2774</v>
+        <v>2138</v>
       </c>
       <c r="D119" t="n">
-        <v>30.0410741839094</v>
+        <v>31.1684661426341</v>
       </c>
       <c r="E119" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B120" s="1" t="n">
-        <v>43070</v>
+        <v>45992</v>
       </c>
       <c r="C120" t="n">
-        <v>1080</v>
+        <v>2129</v>
       </c>
       <c r="D120" t="n">
-        <v>29.9556489974565</v>
+        <v>31.0372611869354</v>
       </c>
       <c r="E120" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="B121" s="1" t="n">
         <v>43435</v>
       </c>
       <c r="C121" t="n">
-        <v>1336</v>
+        <v>2857</v>
       </c>
       <c r="D121" t="n">
-        <v>29.7275942165588</v>
+        <v>30.9399239161605</v>
       </c>
       <c r="E121" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="B122" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="C122" t="n">
-        <v>1070</v>
+        <v>2138</v>
       </c>
       <c r="D122" t="n">
-        <v>29.6782818771097</v>
+        <v>30.5784504591916</v>
       </c>
       <c r="E122" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="123">
@@ -2527,47 +2530,47 @@
         <v>21</v>
       </c>
       <c r="B123" s="1" t="n">
-        <v>42339</v>
+        <v>45627</v>
       </c>
       <c r="C123" t="n">
-        <v>319</v>
+        <v>333</v>
       </c>
       <c r="D123" t="n">
-        <v>29.2138185940918</v>
+        <v>30.4959297549611</v>
       </c>
       <c r="E123" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="B124" s="1" t="n">
         <v>43800</v>
       </c>
       <c r="C124" t="n">
-        <v>317</v>
+        <v>1369</v>
       </c>
       <c r="D124" t="n">
-        <v>29.0306598568248</v>
+        <v>30.4618835946625</v>
       </c>
       <c r="E124" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="B125" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="C125" t="n">
-        <v>285</v>
+        <v>332</v>
       </c>
       <c r="D125" t="n">
-        <v>29.0255954830063</v>
+        <v>30.4043503863276</v>
       </c>
       <c r="E125" t="n">
         <v>10</v>
@@ -2575,19 +2578,19 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B126" s="1" t="n">
-        <v>43800</v>
+        <v>43435</v>
       </c>
       <c r="C126" t="n">
-        <v>609</v>
+        <v>331</v>
       </c>
       <c r="D126" t="n">
-        <v>28.8712342950441</v>
+        <v>30.3127710176941</v>
       </c>
       <c r="E126" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
     </row>
     <row r="127">
@@ -2595,67 +2598,67 @@
         <v>28</v>
       </c>
       <c r="B127" s="1" t="n">
-        <v>43800</v>
+        <v>42339</v>
       </c>
       <c r="C127" t="n">
-        <v>395</v>
+        <v>415</v>
       </c>
       <c r="D127" t="n">
-        <v>28.786415726857</v>
+        <v>30.2439557636599</v>
       </c>
       <c r="E127" t="n">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>30</v>
+        <v>11</v>
       </c>
       <c r="B128" s="1" t="n">
         <v>43070</v>
       </c>
       <c r="C128" t="n">
-        <v>2621</v>
+        <v>409</v>
       </c>
       <c r="D128" t="n">
-        <v>28.3841584124105</v>
+        <v>30.1389930776112</v>
       </c>
       <c r="E128" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>16</v>
+        <v>31</v>
       </c>
       <c r="B129" s="1" t="n">
-        <v>42339</v>
+        <v>43800</v>
       </c>
       <c r="C129" t="n">
-        <v>3336</v>
+        <v>2774</v>
       </c>
       <c r="D129" t="n">
-        <v>28.3434309638219</v>
+        <v>30.0410741839094</v>
       </c>
       <c r="E129" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B130" s="1" t="n">
-        <v>43800</v>
+        <v>43070</v>
       </c>
       <c r="C130" t="n">
-        <v>1304</v>
+        <v>1080</v>
       </c>
       <c r="D130" t="n">
-        <v>27.9990251873133</v>
+        <v>29.9556489974565</v>
       </c>
       <c r="E130" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="131">
@@ -2663,217 +2666,217 @@
         <v>10</v>
       </c>
       <c r="B131" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="C131" t="n">
-        <v>1248</v>
+        <v>1336</v>
       </c>
       <c r="D131" t="n">
-        <v>27.7694892082825</v>
+        <v>29.7275942165588</v>
       </c>
       <c r="E131" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="B132" s="1" t="n">
-        <v>43070</v>
+        <v>43435</v>
       </c>
       <c r="C132" t="n">
-        <v>1835</v>
+        <v>1070</v>
       </c>
       <c r="D132" t="n">
-        <v>27.1797894936413</v>
+        <v>29.6782818771097</v>
       </c>
       <c r="E132" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="B133" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="C133" t="n">
-        <v>974</v>
+        <v>319</v>
       </c>
       <c r="D133" t="n">
-        <v>27.0155575217803</v>
+        <v>29.2138185940918</v>
       </c>
       <c r="E133" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="B134" s="1" t="n">
-        <v>43435</v>
+        <v>43800</v>
       </c>
       <c r="C134" t="n">
-        <v>1837</v>
+        <v>317</v>
       </c>
       <c r="D134" t="n">
-        <v>26.7803892909349</v>
+        <v>29.0306598568248</v>
       </c>
       <c r="E134" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>31</v>
+        <v>8</v>
       </c>
       <c r="B135" s="1" t="n">
-        <v>43435</v>
+        <v>42705</v>
       </c>
       <c r="C135" t="n">
-        <v>1635</v>
+        <v>285</v>
       </c>
       <c r="D135" t="n">
-        <v>26.6220133276149</v>
+        <v>29.0255954830063</v>
       </c>
       <c r="E135" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>32</v>
+        <v>12</v>
       </c>
       <c r="B136" s="1" t="n">
-        <v>43070</v>
+        <v>43800</v>
       </c>
       <c r="C136" t="n">
-        <v>2665</v>
+        <v>609</v>
       </c>
       <c r="D136" t="n">
-        <v>26.4844404657604</v>
+        <v>28.8712342950441</v>
       </c>
       <c r="E136" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>11</v>
+        <v>28</v>
       </c>
       <c r="B137" s="1" t="n">
-        <v>42705</v>
+        <v>43800</v>
       </c>
       <c r="C137" t="n">
-        <v>357</v>
+        <v>395</v>
       </c>
       <c r="D137" t="n">
-        <v>26.3071406569858</v>
+        <v>28.786415726857</v>
       </c>
       <c r="E137" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B138" s="1" t="n">
-        <v>43435</v>
+        <v>43070</v>
       </c>
       <c r="C138" t="n">
-        <v>2575</v>
+        <v>2621</v>
       </c>
       <c r="D138" t="n">
-        <v>25.5900315944965</v>
+        <v>28.3841584124105</v>
       </c>
       <c r="E138" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="B139" s="1" t="n">
         <v>42339</v>
       </c>
       <c r="C139" t="n">
-        <v>3263</v>
+        <v>3336</v>
       </c>
       <c r="D139" t="n">
-        <v>25.1567963055051</v>
+        <v>28.3434309638219</v>
       </c>
       <c r="E139" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="B140" s="1" t="n">
-        <v>42339</v>
+        <v>43800</v>
       </c>
       <c r="C140" t="n">
-        <v>1723</v>
+        <v>1304</v>
       </c>
       <c r="D140" t="n">
-        <v>24.6429701315188</v>
+        <v>27.9990251873133</v>
       </c>
       <c r="E140" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B141" s="1" t="n">
-        <v>42705</v>
+        <v>42339</v>
       </c>
       <c r="C141" t="n">
-        <v>1643</v>
+        <v>1248</v>
       </c>
       <c r="D141" t="n">
-        <v>23.9521935792085</v>
+        <v>27.7694892082825</v>
       </c>
       <c r="E141" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B142" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="C142" t="n">
-        <v>496</v>
+        <v>374</v>
       </c>
       <c r="D142" t="n">
-        <v>23.5141744012182</v>
+        <v>27.5598616406518</v>
       </c>
       <c r="E142" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="B143" s="1" t="n">
-        <v>42705</v>
+        <v>43070</v>
       </c>
       <c r="C143" t="n">
-        <v>494</v>
+        <v>1835</v>
       </c>
       <c r="D143" t="n">
-        <v>23.4193591818584</v>
+        <v>27.1797894936413</v>
       </c>
       <c r="E143" t="n">
         <v>14</v>
@@ -2881,84 +2884,84 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="B144" s="1" t="n">
         <v>42705</v>
       </c>
       <c r="C144" t="n">
-        <v>4996</v>
+        <v>974</v>
       </c>
       <c r="D144" t="n">
-        <v>23.4116950320252</v>
+        <v>27.0155575217803</v>
       </c>
       <c r="E144" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="B145" s="1" t="n">
-        <v>42339</v>
+        <v>43435</v>
       </c>
       <c r="C145" t="n">
-        <v>799</v>
+        <v>1837</v>
       </c>
       <c r="D145" t="n">
-        <v>22.1616329157109</v>
+        <v>26.7803892909349</v>
       </c>
       <c r="E145" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="s">
+        <v>32</v>
+      </c>
+      <c r="B146" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="C146" t="n">
+        <v>1635</v>
+      </c>
+      <c r="D146" t="n">
+        <v>26.6220133276149</v>
+      </c>
+      <c r="E146" t="n">
         <v>14</v>
-      </c>
-      <c r="B146" s="1" t="n">
-        <v>42339</v>
-      </c>
-      <c r="C146" t="n">
-        <v>665</v>
-      </c>
-      <c r="D146" t="n">
-        <v>21.737439192374</v>
-      </c>
-      <c r="E146" t="n">
-        <v>10</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="B147" s="1" t="n">
-        <v>42339</v>
+        <v>43070</v>
       </c>
       <c r="C147" t="n">
-        <v>1320</v>
+        <v>2665</v>
       </c>
       <c r="D147" t="n">
-        <v>21.4684937655982</v>
+        <v>26.4844404657604</v>
       </c>
       <c r="E147" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B148" s="1" t="n">
-        <v>42339</v>
+        <v>42705</v>
       </c>
       <c r="C148" t="n">
-        <v>1455</v>
+        <v>357</v>
       </c>
       <c r="D148" t="n">
-        <v>21.2114678379479</v>
+        <v>26.3071406569858</v>
       </c>
       <c r="E148" t="n">
         <v>12</v>
@@ -2966,52 +2969,307 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="B149" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="C149" t="n">
-        <v>144</v>
+        <v>1176</v>
       </c>
       <c r="D149" t="n">
-        <v>21.0787026058546</v>
+        <v>26.1674032924201</v>
       </c>
       <c r="E149" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="B150" s="1" t="n">
-        <v>42339</v>
+        <v>45992</v>
       </c>
       <c r="C150" t="n">
-        <v>649</v>
+        <v>1314</v>
       </c>
       <c r="D150" t="n">
-        <v>20.0843605034397</v>
+        <v>25.8717285996602</v>
       </c>
       <c r="E150" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s">
+        <v>9</v>
+      </c>
+      <c r="B151" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C151" t="n">
+        <v>1201</v>
+      </c>
+      <c r="D151" t="n">
+        <v>25.7874457438368</v>
+      </c>
+      <c r="E151" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="s">
+        <v>33</v>
+      </c>
+      <c r="B152" s="1" t="n">
+        <v>43435</v>
+      </c>
+      <c r="C152" t="n">
+        <v>2575</v>
+      </c>
+      <c r="D152" t="n">
+        <v>25.5900315944965</v>
+      </c>
+      <c r="E152" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="s">
+        <v>22</v>
+      </c>
+      <c r="B153" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3263</v>
+      </c>
+      <c r="D153" t="n">
+        <v>25.1567963055051</v>
+      </c>
+      <c r="E153" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="s">
+        <v>29</v>
+      </c>
+      <c r="B154" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C154" t="n">
+        <v>1723</v>
+      </c>
+      <c r="D154" t="n">
+        <v>24.6429701315188</v>
+      </c>
+      <c r="E154" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="s">
+        <v>7</v>
+      </c>
+      <c r="B155" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="C155" t="n">
+        <v>1643</v>
+      </c>
+      <c r="D155" t="n">
+        <v>23.9521935792085</v>
+      </c>
+      <c r="E155" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="s">
+        <v>20</v>
+      </c>
+      <c r="B156" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="C156" t="n">
+        <v>853</v>
+      </c>
+      <c r="D156" t="n">
+        <v>23.6594153655837</v>
+      </c>
+      <c r="E156" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="s">
+        <v>12</v>
+      </c>
+      <c r="B157" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C157" t="n">
+        <v>496</v>
+      </c>
+      <c r="D157" t="n">
+        <v>23.5141744012182</v>
+      </c>
+      <c r="E157" t="n">
         <v>8</v>
       </c>
-      <c r="B151" s="1" t="n">
+    </row>
+    <row r="158">
+      <c r="A158" t="s">
+        <v>12</v>
+      </c>
+      <c r="B158" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="C158" t="n">
+        <v>494</v>
+      </c>
+      <c r="D158" t="n">
+        <v>23.4193591818584</v>
+      </c>
+      <c r="E158" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="s">
+        <v>27</v>
+      </c>
+      <c r="B159" s="1" t="n">
+        <v>42705</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4996</v>
+      </c>
+      <c r="D159" t="n">
+        <v>23.4116950320252</v>
+      </c>
+      <c r="E159" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="s">
+        <v>20</v>
+      </c>
+      <c r="B160" s="1" t="n">
         <v>42339</v>
       </c>
-      <c r="C151" t="n">
+      <c r="C160" t="n">
+        <v>799</v>
+      </c>
+      <c r="D160" t="n">
+        <v>22.1616329157109</v>
+      </c>
+      <c r="E160" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="s">
+        <v>14</v>
+      </c>
+      <c r="B161" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C161" t="n">
+        <v>665</v>
+      </c>
+      <c r="D161" t="n">
+        <v>21.737439192374</v>
+      </c>
+      <c r="E161" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="s">
+        <v>18</v>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C162" t="n">
+        <v>1320</v>
+      </c>
+      <c r="D162" t="n">
+        <v>21.4684937655982</v>
+      </c>
+      <c r="E162" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="s">
+        <v>7</v>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C163" t="n">
+        <v>1455</v>
+      </c>
+      <c r="D163" t="n">
+        <v>21.2114678379479</v>
+      </c>
+      <c r="E163" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="s">
+        <v>5</v>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C164" t="n">
+        <v>144</v>
+      </c>
+      <c r="D164" t="n">
+        <v>21.0787026058546</v>
+      </c>
+      <c r="E164" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="s">
+        <v>34</v>
+      </c>
+      <c r="B165" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C165" t="n">
+        <v>649</v>
+      </c>
+      <c r="D165" t="n">
+        <v>20.0843605034397</v>
+      </c>
+      <c r="E165" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="s">
+        <v>8</v>
+      </c>
+      <c r="B166" s="1" t="n">
+        <v>42339</v>
+      </c>
+      <c r="C166" t="n">
         <v>195</v>
       </c>
-      <c r="D151" t="n">
+      <c r="D166" t="n">
         <v>19.8596179620569</v>
       </c>
-      <c r="E151" t="n">
+      <c r="E166" t="n">
         <v>15</v>
       </c>
     </row>
